--- a/data/trans_camb/P8_1_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P8_1_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 6,4</t>
+          <t>-2,02; 6,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 4,84</t>
+          <t>-2,65; 5,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 1,66</t>
+          <t>-5,63; 1,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 2,16</t>
+          <t>-8,25; 2,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 2,58</t>
+          <t>-8,01; 2,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 2,21</t>
+          <t>-7,46; 2,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 3,62</t>
+          <t>-3,07; 3,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 2,47</t>
+          <t>-3,89; 3,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 0,78</t>
+          <t>-4,86; 0,95</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 91,32</t>
+          <t>-18,82; 86,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,72; 67,04</t>
+          <t>-24,0; 77,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 23,95</t>
+          <t>-50,47; 20,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-48,7; 21,28</t>
+          <t>-48,03; 25,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,24; 21,94</t>
+          <t>-45,15; 26,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,59; 22,07</t>
+          <t>-41,01; 20,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 37,52</t>
+          <t>-24,16; 38,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,93; 25,62</t>
+          <t>-29,45; 31,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,79; 9,0</t>
+          <t>-36,14; 9,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 11,53</t>
+          <t>2,74; 11,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,81</t>
+          <t>0,36; 8,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 10,09</t>
+          <t>2,24; 10,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,73</t>
+          <t>0,67; 9,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 9,25</t>
+          <t>0,23; 8,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 12,09</t>
+          <t>4,92; 12,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,03</t>
+          <t>3,0; 8,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,5</t>
+          <t>1,87; 7,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 10,04</t>
+          <t>4,39; 9,99</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,17; 283,8</t>
+          <t>31,28; 332,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,01; 239,04</t>
+          <t>4,39; 242,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,44; 271,71</t>
+          <t>24,79; 290,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,27; 220,18</t>
+          <t>8,68; 234,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 215,14</t>
+          <t>1,64; 218,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,6; 307,64</t>
+          <t>60,8; 307,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,5; 203,82</t>
+          <t>37,83; 195,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,67; 168,99</t>
+          <t>26,8; 165,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,32; 239,56</t>
+          <t>65,32; 240,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 9,54</t>
+          <t>0,8; 9,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 7,01</t>
+          <t>-1,09; 7,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 70,24</t>
+          <t>3,54; 67,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 9,52</t>
+          <t>-8,68; 9,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 9,75</t>
+          <t>-9,16; 9,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 12,09</t>
+          <t>-4,32; 11,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,52</t>
+          <t>0,91; 8,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 6,18</t>
+          <t>-1,45; 6,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 60,56</t>
+          <t>4,29; 59,17</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,36; 99,03</t>
+          <t>5,4; 98,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 71,64</t>
+          <t>-9,27; 74,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,75; 697,28</t>
+          <t>27,73; 722,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 48,82</t>
+          <t>-29,31; 49,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 49,29</t>
+          <t>-33,48; 50,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 63,29</t>
+          <t>-15,35; 62,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,01; 67,78</t>
+          <t>5,37; 66,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 48,85</t>
+          <t>-9,45; 48,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,66; 489,5</t>
+          <t>28,22; 486,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 5,61</t>
+          <t>-0,41; 5,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,17</t>
+          <t>-1,87; 3,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 7,12</t>
+          <t>0,62; 6,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 1,1</t>
+          <t>-6,46; 1,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 1,95</t>
+          <t>-5,85; 2,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,5; -1,53</t>
+          <t>-12,81; -1,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,98</t>
+          <t>-1,93; 2,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 2,26</t>
+          <t>-2,29; 2,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 2,42</t>
+          <t>-5,82; 2,28</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 42,33</t>
+          <t>-3,01; 42,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 31,38</t>
+          <t>-11,63; 30,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,01; 53,69</t>
+          <t>3,83; 49,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,24; 6,99</t>
+          <t>-32,01; 7,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 12,23</t>
+          <t>-28,02; 11,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,82; -8,73</t>
+          <t>-62,26; -7,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 20,09</t>
+          <t>-11,13; 18,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 14,79</t>
+          <t>-13,68; 16,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 15,54</t>
+          <t>-34,41; 14,96</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 8,25</t>
+          <t>-1,57; 8,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 10,58</t>
+          <t>0,65; 10,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 11,82</t>
+          <t>1,56; 12,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,63; 18,75</t>
+          <t>8,57; 18,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,22; 13,4</t>
+          <t>3,69; 13,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 11,4</t>
+          <t>-1,9; 11,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,37; 12,65</t>
+          <t>5,58; 12,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,47; 10,34</t>
+          <t>3,93; 10,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,67; 10,12</t>
+          <t>1,87; 10,37</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 71,97</t>
+          <t>-9,96; 72,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,69; 92,27</t>
+          <t>4,68; 90,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8,98; 102,97</t>
+          <t>8,56; 107,88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38,33; 108,01</t>
+          <t>37,23; 107,28</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>18,51; 78,5</t>
+          <t>17,45; 81,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 62,23</t>
+          <t>-8,2; 65,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,26; 80,19</t>
+          <t>28,2; 80,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18,18; 66,84</t>
+          <t>19,47; 69,54</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>9,16; 62,36</t>
+          <t>10,79; 66,07</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 4,35</t>
+          <t>-1,58; 4,56</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 2,05</t>
+          <t>-2,77; 2,28</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,13</t>
+          <t>-3,42; 1,49</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,85; 8,46</t>
+          <t>0,85; 8,83</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 4,52</t>
+          <t>-3,51; 4,55</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 5,87</t>
+          <t>-1,52; 5,91</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,6; 7,19</t>
+          <t>0,39; 7,06</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,92</t>
+          <t>-3,05; 3,25</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 3,15</t>
+          <t>-3,43; 3,37</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 275,09</t>
+          <t>-48,43; 368,43</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-77,28; 163,79</t>
+          <t>-76,75; 180,88</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-82,57; 121,1</t>
+          <t>-81,89; 140,24</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2,75; 30,39</t>
+          <t>2,68; 31,12</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 16,14</t>
+          <t>-11,15; 16,49</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 21,13</t>
+          <t>-4,74; 21,67</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,34; 31,17</t>
+          <t>1,23; 30,24</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 12,57</t>
+          <t>-11,82; 14,46</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 13,48</t>
+          <t>-13,34; 14,69</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,18</t>
+          <t>1,78; 5,16</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,45</t>
+          <t>1,01; 4,25</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,82; 27,46</t>
+          <t>2,88; 25,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,94</t>
+          <t>1,98; 5,88</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,17</t>
+          <t>-0,97; 3,1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,57</t>
+          <t>-4,31; 1,72</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,02</t>
+          <t>2,4; 4,99</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,24</t>
+          <t>0,64; 3,24</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,96; 16,68</t>
+          <t>1,06; 14,27</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>15,14; 50,36</t>
+          <t>13,84; 49,37</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>9,26; 43,57</t>
+          <t>8,54; 41,13</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24,76; 245,32</t>
+          <t>25,41; 229,89</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7,93; 29,68</t>
+          <t>8,98; 28,97</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 15,66</t>
+          <t>-4,05; 15,26</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 7,49</t>
+          <t>-19,35; 8,2</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,94; 31,6</t>
+          <t>14,29; 31,8</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>3,66; 20,54</t>
+          <t>3,68; 20,65</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>5,72; 103,31</t>
+          <t>6,49; 87,25</t>
         </is>
       </c>
     </row>
